--- a/data/ams_weekly_data/Nexlev/ads_report_week30.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week30.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -770,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -857,10 +846,10 @@
         <v>23900</v>
       </c>
       <c r="G15" t="n">
-        <v>25170.33</v>
+        <v>27406.77</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -994,10 +983,10 @@
         <v>2063</v>
       </c>
       <c r="F20" t="n">
-        <v>319519</v>
+        <v>319517</v>
       </c>
       <c r="G20" t="n">
-        <v>191829.63</v>
+        <v>191829.62</v>
       </c>
       <c r="H20" t="n">
         <v>37</v>
@@ -1078,7 +1067,7 @@
         <v>1338</v>
       </c>
       <c r="F23" t="n">
-        <v>106346</v>
+        <v>106345</v>
       </c>
       <c r="G23" t="n">
         <v>24094.92</v>
@@ -1274,7 +1263,7 @@
         <v>631</v>
       </c>
       <c r="F30" t="n">
-        <v>32827</v>
+        <v>32825</v>
       </c>
       <c r="G30" t="n">
         <v>51256.71</v>
@@ -1414,7 +1403,7 @@
         <v>157</v>
       </c>
       <c r="F35" t="n">
-        <v>21292</v>
+        <v>21287</v>
       </c>
       <c r="G35" t="n">
         <v>21184.74</v>
@@ -1722,7 +1711,7 @@
         <v>250</v>
       </c>
       <c r="F46" t="n">
-        <v>40802</v>
+        <v>40801</v>
       </c>
       <c r="G46" t="n">
         <v>10574.58</v>
@@ -1809,10 +1798,10 @@
         <v>38849</v>
       </c>
       <c r="G49" t="n">
-        <v>23716.97</v>
+        <v>25411.04</v>
       </c>
       <c r="H49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -1946,7 +1935,7 @@
         <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>14238</v>
+        <v>14237</v>
       </c>
       <c r="G54" t="n">
         <v>1863.56</v>
@@ -1974,7 +1963,7 @@
         <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>68998</v>
+        <v>68993</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2002,7 +1991,7 @@
         <v>195</v>
       </c>
       <c r="F56" t="n">
-        <v>132999</v>
+        <v>132998</v>
       </c>
       <c r="G56" t="n">
         <v>1863.56</v>
@@ -2061,10 +2050,10 @@
         <v>59543</v>
       </c>
       <c r="G58" t="n">
-        <v>20333.88</v>
+        <v>23722.86</v>
       </c>
       <c r="H58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -2450,7 +2439,7 @@
         <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>17185</v>
+        <v>17184</v>
       </c>
       <c r="G72" t="n">
         <v>1481.36</v>
@@ -2590,13 +2579,13 @@
         <v>346</v>
       </c>
       <c r="F77" t="n">
-        <v>38861</v>
+        <v>38860</v>
       </c>
       <c r="G77" t="n">
-        <v>54634.76</v>
+        <v>59718.66</v>
       </c>
       <c r="H77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -2677,10 +2666,10 @@
         <v>183050</v>
       </c>
       <c r="G80" t="n">
-        <v>26667.81</v>
+        <v>28361.87</v>
       </c>
       <c r="H80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -2730,7 +2719,7 @@
         <v>429</v>
       </c>
       <c r="F82" t="n">
-        <v>63418</v>
+        <v>63416</v>
       </c>
       <c r="G82" t="n">
         <v>23716.97</v>
@@ -2789,10 +2778,10 @@
         <v>5234</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2965.25</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2845,10 +2834,10 @@
         <v>183093</v>
       </c>
       <c r="G86" t="n">
-        <v>113985.49</v>
+        <v>116950.74</v>
       </c>
       <c r="H86" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
@@ -2982,7 +2971,7 @@
         <v>131</v>
       </c>
       <c r="F91" t="n">
-        <v>48186</v>
+        <v>48185</v>
       </c>
       <c r="G91" t="n">
         <v>4066.1</v>
@@ -3156,7 +3145,7 @@
         <v>10168.64</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -3682,7 +3671,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="n">
-        <v>12773</v>
+        <v>12772</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4158,7 +4147,7 @@
         <v>10</v>
       </c>
       <c r="F133" t="n">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="G133" t="n">
         <v>1248.31</v>
@@ -4298,7 +4287,7 @@
         <v>44</v>
       </c>
       <c r="F138" t="n">
-        <v>5036</v>
+        <v>5035</v>
       </c>
       <c r="G138" t="n">
         <v>1301.9</v>
@@ -4326,7 +4315,7 @@
         <v>65</v>
       </c>
       <c r="F139" t="n">
-        <v>11042</v>
+        <v>11041</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4662,7 +4651,7 @@
         <v>1262</v>
       </c>
       <c r="F151" t="n">
-        <v>109020</v>
+        <v>109017</v>
       </c>
       <c r="G151" t="n">
         <v>50843.2</v>
@@ -6202,7 +6191,7 @@
         <v>791</v>
       </c>
       <c r="F206" t="n">
-        <v>196004</v>
+        <v>196003</v>
       </c>
       <c r="G206" t="n">
         <v>18215.23</v>
@@ -6345,10 +6334,10 @@
         <v>33798</v>
       </c>
       <c r="G211" t="n">
-        <v>11561</v>
+        <v>14441.51</v>
       </c>
       <c r="H211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -6394,42 +6383,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -6448,13 +6437,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1285.28</v>
+        <v>1281.5</v>
       </c>
       <c r="E2" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F2" t="n">
-        <v>222568</v>
+        <v>222567</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -7721,6 +7710,1453 @@
       </c>
       <c r="H47" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>638</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" t="n">
+        <v>382.7361368220043</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2541.530000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4326</v>
+      </c>
+      <c r="E3" t="n">
+        <v>154</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2595.043863177996</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17232.19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0FPGDVVCX</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>27377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1926.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4994.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3758</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>232.3367777734329</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1046.67</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0DCGHKRXX</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5778</v>
+      </c>
+      <c r="E6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>357.2321965914194</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1609.32</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17091</v>
+      </c>
+      <c r="E7" t="n">
+        <v>102</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1056.611025635148</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4760</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1753</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>264.98</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2285</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>550.5500000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10166.94</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20262</v>
+      </c>
+      <c r="E10" t="n">
+        <v>335</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3695.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17816.11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>23873</v>
+      </c>
+      <c r="E11" t="n">
+        <v>388</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4658.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7624.58</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7013</v>
+      </c>
+      <c r="E12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1332.64</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10167.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1762</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3859.649711584453</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2251.190288415547</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2965.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4858</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37</v>
+      </c>
+      <c r="F15" t="n">
+        <v>431.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- Exact 01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2388</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>249.28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>42988</v>
+      </c>
+      <c r="E17" t="n">
+        <v>324</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4724.02</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-Exact- SBV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6846</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>255.07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01-SBV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13265</v>
+      </c>
+      <c r="E19" t="n">
+        <v>177</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2573.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-Phrase- SBV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>27867</v>
+      </c>
+      <c r="E20" t="n">
+        <v>173</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2722.43</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-SBV-PT01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15951</v>
+      </c>
+      <c r="E21" t="n">
+        <v>158</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3893.82</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>42318</v>
+      </c>
+      <c r="E22" t="n">
+        <v>119</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1184.748516245692</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8499.277816258413</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>93357</v>
+      </c>
+      <c r="E23" t="n">
+        <v>261</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2613.621483754308</v>
+      </c>
+      <c r="G23" t="n">
+        <v>18749.88218374159</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15271</v>
+      </c>
+      <c r="E26" t="n">
+        <v>705</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6785.711962257038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>72933.92671422615</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12785</v>
+      </c>
+      <c r="E27" t="n">
+        <v>591</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5681.322313232748</v>
+      </c>
+      <c r="G27" t="n">
+        <v>61063.76862707148</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13361</v>
+      </c>
+      <c r="E28" t="n">
+        <v>617</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5937.285724510213</v>
+      </c>
+      <c r="G28" t="n">
+        <v>63814.90465870236</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E29" t="n">
+        <v>162</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2149.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10166.94</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>18109</v>
+      </c>
+      <c r="E30" t="n">
+        <v>240</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2725.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3388.98</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>462</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5685</v>
+      </c>
+      <c r="E32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F32" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>535</v>
+      </c>
+      <c r="E33" t="n">
+        <v>23</v>
+      </c>
+      <c r="F33" t="n">
+        <v>155.36</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15405</v>
+      </c>
+      <c r="E34" t="n">
+        <v>230</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2121.12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5735.59</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7818</v>
+      </c>
+      <c r="E35" t="n">
+        <v>245</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3300.725439799365</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7240.608201981877</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13679</v>
+      </c>
+      <c r="E36" t="n">
+        <v>430</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5775.584560200634</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12669.56179801812</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6683</v>
+      </c>
+      <c r="E37" t="n">
+        <v>84</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1120.05567567296</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>19491</v>
+      </c>
+      <c r="E38" t="n">
+        <v>245</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3266.434324327039</v>
+      </c>
+      <c r="G38" t="n">
+        <v>14826.25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev_B0GN8WW6BC_Stand Mixer_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20640</v>
+      </c>
+      <c r="E39" t="n">
+        <v>195</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2062.28</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1531</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" t="n">
+        <v>268.56</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>37347</v>
+      </c>
+      <c r="E41" t="n">
+        <v>419</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5134.29</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5295</v>
+      </c>
+      <c r="E42" t="n">
+        <v>128</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2121.72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-02</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28</v>
+      </c>
+      <c r="F43" t="n">
+        <v>450.02</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ams_weekly_data/Nexlev/ads_report_week30.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week30.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -846,10 +858,10 @@
         <v>23900</v>
       </c>
       <c r="G15" t="n">
-        <v>27406.77</v>
+        <v>25170.33</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -986,10 +998,10 @@
         <v>319517</v>
       </c>
       <c r="G20" t="n">
-        <v>191829.62</v>
+        <v>196489.79</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -2050,10 +2062,10 @@
         <v>59543</v>
       </c>
       <c r="G58" t="n">
-        <v>23722.86</v>
+        <v>20333.88</v>
       </c>
       <c r="H58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -2778,10 +2790,10 @@
         <v>5234</v>
       </c>
       <c r="G84" t="n">
-        <v>2965.25</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3145,7 +3157,7 @@
         <v>10168.64</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6334,10 +6346,10 @@
         <v>33798</v>
       </c>
       <c r="G211" t="n">
-        <v>14441.51</v>
+        <v>11561</v>
       </c>
       <c r="H211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -6383,42 +6395,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -7727,47 +7739,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
